--- a/Data/trashbin_photo_metadata.xlsx
+++ b/Data/trashbin_photo_metadata.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,65 +458,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IMG_0490.HEIC</t>
+          <t>IndigoCt.jpg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026:08:22 16:05:30</t>
+          <t>2026:03:01 14:41:09</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>41.629892</v>
+        <v>41.629889</v>
       </c>
       <c r="D2" t="n">
-        <v>-91.49893899999999</v>
+        <v>-91.49899000000001</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro</t>
+          <t>Galaxy A25 5G</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IMG_0504.HEIC</t>
+          <t>Wetherby1.jpg</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026:08:23 16:57:09</t>
+          <t>2026:06:07 08:43:24</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>41.625256</v>
+        <v>41.634505</v>
       </c>
       <c r="D3" t="n">
-        <v>-91.526314</v>
+        <v>-91.518136</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro</t>
+          <t>Galaxy A25 5G</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IMG_0505.HEIC</t>
+          <t>IMG_0490.HEIC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026:08:23 16:58:40</t>
+          <t>2026:08:22 16:05:30</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>41.626358</v>
+        <v>41.629892</v>
       </c>
       <c r="D4" t="n">
-        <v>-91.528306</v>
+        <v>-91.49893899999999</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -527,19 +527,19 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IMG_0506.HEIC</t>
+          <t>IMG_0504.HEIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026:08:23 16:59:51</t>
+          <t>2026:08:23 16:57:09</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>41.626808</v>
+        <v>41.625256</v>
       </c>
       <c r="D5" t="n">
-        <v>-91.52976099999999</v>
+        <v>-91.526314</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -550,19 +550,19 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IMG_0507.HEIC</t>
+          <t>IMG_0505.HEIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026:08:23 17:01:31</t>
+          <t>2026:08:23 16:58:40</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>41.627286</v>
+        <v>41.626358</v>
       </c>
       <c r="D6" t="n">
-        <v>-91.53085299999999</v>
+        <v>-91.528306</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -573,19 +573,19 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IMG_0510.HEIC</t>
+          <t>IMG_0506.HEIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026:08:23 17:12:40</t>
+          <t>2026:08:23 16:59:51</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>41.649053</v>
+        <v>41.626808</v>
       </c>
       <c r="D7" t="n">
-        <v>-91.535369</v>
+        <v>-91.52976099999999</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -596,19 +596,19 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IMG_0515.HEIC</t>
+          <t>IMG_0507.HEIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026:08:23 17:33:42</t>
+          <t>2026:08:23 17:01:31</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>41.675683</v>
+        <v>41.627286</v>
       </c>
       <c r="D8" t="n">
-        <v>-91.54296100000001</v>
+        <v>-91.53085299999999</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -619,19 +619,19 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IMG_0516.HEIC</t>
+          <t>IMG_0510.HEIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026:08:23 17:34:02</t>
+          <t>2026:08:23 17:12:40</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>41.675608</v>
+        <v>41.649053</v>
       </c>
       <c r="D9" t="n">
-        <v>-91.542839</v>
+        <v>-91.535369</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -642,19 +642,19 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IMG_0517.HEIC</t>
+          <t>IMG_0515.HEIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026:08:23 17:34:22</t>
+          <t>2026:08:23 17:33:42</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>41.675758</v>
+        <v>41.675683</v>
       </c>
       <c r="D10" t="n">
-        <v>-91.542733</v>
+        <v>-91.54296100000001</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -665,19 +665,19 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IMG_0518.HEIC</t>
+          <t>IMG_0516.HEIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026:08:23 17:34:33</t>
+          <t>2026:08:23 17:34:02</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>41.675769</v>
+        <v>41.675608</v>
       </c>
       <c r="D11" t="n">
-        <v>-91.54276400000001</v>
+        <v>-91.542839</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -688,19 +688,19 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IMG_0519.HEIC</t>
+          <t>IMG_0517.HEIC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026:08:23 17:35:17</t>
+          <t>2026:08:23 17:34:22</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>41.675756</v>
+        <v>41.675758</v>
       </c>
       <c r="D12" t="n">
-        <v>-91.542314</v>
+        <v>-91.542733</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -711,19 +711,19 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IMG_0520.HEIC</t>
+          <t>IMG_0518.HEIC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026:08:23 17:35:20</t>
+          <t>2026:08:23 17:34:33</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>41.675756</v>
+        <v>41.675769</v>
       </c>
       <c r="D13" t="n">
-        <v>-91.542314</v>
+        <v>-91.54276400000001</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -734,16 +734,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IMG_0521.HEIC</t>
+          <t>IMG_0519.HEIC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026:08:23 17:35:37</t>
+          <t>2026:08:23 17:35:17</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>41.675769</v>
+        <v>41.675756</v>
       </c>
       <c r="D14" t="n">
         <v>-91.542314</v>
@@ -757,19 +757,19 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IMG_0522.HEIC</t>
+          <t>IMG_0520.HEIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026:08:23 17:36:03</t>
+          <t>2026:08:23 17:35:20</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>41.675953</v>
+        <v>41.675756</v>
       </c>
       <c r="D15" t="n">
-        <v>-91.54220599999999</v>
+        <v>-91.542314</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -780,19 +780,19 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IMG_0523.HEIC</t>
+          <t>IMG_0521.HEIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026:08:23 17:36:09</t>
+          <t>2026:08:23 17:35:37</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>41.675761</v>
+        <v>41.675769</v>
       </c>
       <c r="D16" t="n">
-        <v>-91.542244</v>
+        <v>-91.542314</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -803,19 +803,19 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IMG_0524.HEIC</t>
+          <t>IMG_0522.HEIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026:08:23 17:36:15</t>
+          <t>2026:08:23 17:36:03</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>41.675731</v>
+        <v>41.675953</v>
       </c>
       <c r="D17" t="n">
-        <v>-91.542192</v>
+        <v>-91.54220599999999</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -826,19 +826,19 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IMG_0526.HEIC</t>
+          <t>IMG_0523.HEIC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026:08:23 17:51:27</t>
+          <t>2026:08:23 17:36:09</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>41.667369</v>
+        <v>41.675761</v>
       </c>
       <c r="D18" t="n">
-        <v>-91.557306</v>
+        <v>-91.542244</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -849,19 +849,19 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IMG_0531.HEIC</t>
+          <t>IMG_0524.HEIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026:08:24 18:14:13</t>
+          <t>2026:08:23 17:36:15</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>41.634067</v>
+        <v>41.675731</v>
       </c>
       <c r="D19" t="n">
-        <v>-91.532319</v>
+        <v>-91.542192</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -872,19 +872,19 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IMG_0532.HEIC</t>
+          <t>IMG_0526.HEIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026:08:24 18:14:34</t>
+          <t>2026:08:23 17:51:27</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>41.634139</v>
+        <v>41.667369</v>
       </c>
       <c r="D20" t="n">
-        <v>-91.532264</v>
+        <v>-91.557306</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -895,65 +895,65 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IMG_0533.HEIC</t>
+          <t>SycGreenway1.jpg</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026:08:24 18:15:18</t>
+          <t>2026:08:24 16:00:03</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>41.634725</v>
+        <v>41.630557</v>
       </c>
       <c r="D21" t="n">
-        <v>-91.53225</v>
+        <v>-91.507088</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro</t>
+          <t>Galaxy A25 5G</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IMG_0534.HEIC</t>
+          <t>SycGreenway2.jpg</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026:08:24 18:15:41</t>
+          <t>2026:08:24 16:27:26</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>41.634811</v>
+        <v>41.627624</v>
       </c>
       <c r="D22" t="n">
-        <v>-91.532211</v>
+        <v>-91.511647</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro</t>
+          <t>Galaxy A25 5G</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IMG_0535.HEIC</t>
+          <t>IMG_0531.HEIC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026:08:24 18:17:16</t>
+          <t>2026:08:24 18:14:13</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>41.633822</v>
+        <v>41.634067</v>
       </c>
       <c r="D23" t="n">
-        <v>-91.531311</v>
+        <v>-91.532319</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -964,19 +964,19 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IMG_0536.HEIC</t>
+          <t>IMG_0532.HEIC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026:08:24 18:17:39</t>
+          <t>2026:08:24 18:14:34</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>41.633669</v>
+        <v>41.634139</v>
       </c>
       <c r="D24" t="n">
-        <v>-91.531294</v>
+        <v>-91.532264</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -987,19 +987,19 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IMG_0538.HEIC</t>
+          <t>IMG_0533.HEIC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026:08:24 18:20:43</t>
+          <t>2026:08:24 18:15:18</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>41.629272</v>
+        <v>41.634725</v>
       </c>
       <c r="D25" t="n">
-        <v>-91.52786399999999</v>
+        <v>-91.53225</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1010,19 +1010,19 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IMG_0539.HEIC</t>
+          <t>IMG_0534.HEIC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026:08:24 18:20:54</t>
+          <t>2026:08:24 18:15:41</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>41.6328</v>
+        <v>41.634811</v>
       </c>
       <c r="D26" t="n">
-        <v>-91.53135</v>
+        <v>-91.532211</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1033,19 +1033,19 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IMG_0540.HEIC</t>
+          <t>IMG_0535.HEIC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026:08:24 18:21:14</t>
+          <t>2026:08:24 18:17:16</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>41.632739</v>
+        <v>41.633822</v>
       </c>
       <c r="D27" t="n">
-        <v>-91.531289</v>
+        <v>-91.531311</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1056,19 +1056,19 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IMG_0541.HEIC</t>
+          <t>IMG_0536.HEIC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026:08:24 18:21:26</t>
+          <t>2026:08:24 18:17:39</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>41.632736</v>
+        <v>41.633669</v>
       </c>
       <c r="D28" t="n">
-        <v>-91.53135</v>
+        <v>-91.531294</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1079,19 +1079,19 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IMG_0542.HEIC</t>
+          <t>IMG_0538.HEIC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026:08:24 18:22:33</t>
+          <t>2026:08:24 18:20:43</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>41.632233</v>
+        <v>41.629272</v>
       </c>
       <c r="D29" t="n">
-        <v>-91.530883</v>
+        <v>-91.52786399999999</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1102,19 +1102,19 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IMG_0543.HEIC</t>
+          <t>IMG_0539.HEIC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026:08:24 18:24:43</t>
+          <t>2026:08:24 18:20:54</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>41.630731</v>
+        <v>41.6328</v>
       </c>
       <c r="D30" t="n">
-        <v>-91.53147199999999</v>
+        <v>-91.53135</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1125,19 +1125,19 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IMG_0548.HEIC</t>
+          <t>IMG_0540.HEIC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026:08:24 18:35:56</t>
+          <t>2026:08:24 18:21:14</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>41.620564</v>
+        <v>41.632739</v>
       </c>
       <c r="D31" t="n">
-        <v>-91.523619</v>
+        <v>-91.531289</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1148,19 +1148,19 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IMG_0554.HEIC</t>
+          <t>IMG_0541.HEIC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026:08:24 18:48:02</t>
+          <t>2026:08:24 18:21:26</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>41.626869</v>
+        <v>41.632736</v>
       </c>
       <c r="D32" t="n">
-        <v>-91.52758900000001</v>
+        <v>-91.53135</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1171,21 +1171,205 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>IMG_0542.HEIC</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026:08:24 18:22:33</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>41.632233</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-91.530883</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>iPhone 17 Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>IMG_0543.HEIC</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026:08:24 18:24:43</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>41.630731</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-91.53147199999999</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>iPhone 17 Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>IMG_0548.HEIC</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026:08:24 18:35:56</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>41.620564</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-91.523619</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>iPhone 17 Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>IMG_0554.HEIC</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026:08:24 18:48:02</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>41.626869</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-91.52758900000001</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>iPhone 17 Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>IMG_0572.HEIC</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>2026:08:24 19:20:19</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="C37" t="n">
         <v>41.651781</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D37" t="n">
         <v>-91.52712200000001</v>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>iPhone 17 Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Fairmeadows.jpg</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026:08:29 16:21:51</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>41.633849</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-91.505377</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Galaxy A25 5G</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>IMG_0694.jpg</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026:09:11 18:07:40</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>41.666736</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-91.52758900000001</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>iPhone 17 Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>IMG_0908.HEIC</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026:09:17 17:47:25</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>41.670953</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-91.52413900000001</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>iPhone 17 Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>IMG_1153.jpg</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026:10:10 17:11:47</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>41.621442</v>
+      </c>
+      <c r="D41" t="n">
+        <v>-91.529031</v>
+      </c>
+      <c r="E41" t="inlineStr">
         <is>
           <t>iPhone 17 Pro</t>
         </is>
